--- a/thalamus_channels.xlsx
+++ b/thalamus_channels.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/barbora/Projekty/arousal/Sana/nature_submission_code/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ANPHY2\Workspace\Barbora\Hannan_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D4B313-BE34-9B41-9999-A0BFB221C1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5488D1-9A8C-42DF-9A31-DED68F8CFB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="26620" windowHeight="16280" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12645" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="channels_bipolar" sheetId="4" r:id="rId1"/>
@@ -115,7 +115,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normální" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -448,12 +448,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -461,7 +461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -469,7 +469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -477,7 +477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -485,7 +485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -493,7 +493,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -501,7 +501,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -509,7 +509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -517,7 +517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -538,9 +538,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83EB10EC-058D-1F49-A38A-7B2D1238154F}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,114 +552,114 @@
       </c>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>125100</v>
+        <v>12217</v>
       </c>
       <c r="C2" s="1">
-        <v>125677</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>12273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>644171</v>
+        <v>62907</v>
       </c>
       <c r="C3" s="1">
-        <v>644514</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>62941</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>903645</v>
+        <v>88247</v>
       </c>
       <c r="C4" s="1">
-        <v>903887</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88270</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="1">
-        <v>1163161</v>
+        <v>113590</v>
       </c>
       <c r="C5" s="1">
-        <v>1171830</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>114437</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="1">
-        <v>1422505</v>
+        <v>138917</v>
       </c>
       <c r="C6" s="1">
-        <v>1422859</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+        <v>138951</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="1">
-        <v>736571</v>
+        <v>71931</v>
       </c>
       <c r="C7" s="1">
-        <v>738129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>72083</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="1">
-        <v>995854</v>
+        <v>97251</v>
       </c>
       <c r="C8" s="1">
-        <v>997329</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+        <v>97395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="1">
-        <v>1514635</v>
+        <v>147914</v>
       </c>
       <c r="C9" s="1">
-        <v>1515766</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>148024</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="1">
-        <v>2033338</v>
+        <v>198568</v>
       </c>
       <c r="C10" s="1">
-        <v>2035218</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>198752</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="1">
-        <v>2676023</v>
+        <v>261330</v>
       </c>
       <c r="C11" s="1">
-        <v>2677365</v>
+        <v>261461</v>
       </c>
     </row>
   </sheetData>

--- a/thalamus_channels.xlsx
+++ b/thalamus_channels.xlsx
@@ -1,34 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ANPHY2\Workspace\Barbora\Hannan_code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/barbora/Projekty/arousal/Sana/nature_submission_code/Hannan_code_v2/Hannan_code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5488D1-9A8C-42DF-9A31-DED68F8CFB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870BAB1D-E66C-6A45-9D44-1E7F23EE486D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12645" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="16380" windowHeight="8200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="channels_bipolar" sheetId="4" r:id="rId1"/>
-    <sheet name="arousal" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -37,57 +25,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="14">
   <si>
     <t>patient</t>
   </si>
   <si>
-    <t>channel</t>
+    <t>ID</t>
   </si>
   <si>
     <t>P11</t>
   </si>
   <si>
+    <t>DEP0032</t>
+  </si>
+  <si>
+    <t>LTPS1</t>
+  </si>
+  <si>
+    <t>LTPS2</t>
+  </si>
+  <si>
+    <t>LTPS3</t>
+  </si>
+  <si>
+    <t>LTPS4</t>
+  </si>
+  <si>
+    <t>LTPS5</t>
+  </si>
+  <si>
+    <t>LTPS6</t>
+  </si>
+  <si>
     <t>P14</t>
   </si>
   <si>
-    <t>LTPS1-LTPS2</t>
-  </si>
-  <si>
-    <t>LTPS2-LTPS3</t>
-  </si>
-  <si>
-    <t>LTPS3-LTPS4</t>
-  </si>
-  <si>
-    <t>LTPS4-LTPS5</t>
-  </si>
-  <si>
-    <t>LTPS5-LTPS6</t>
-  </si>
-  <si>
-    <t>stim_start</t>
-  </si>
-  <si>
-    <t>arousal_start</t>
+    <t>DEP0067</t>
+  </si>
+  <si>
+    <t>channel1</t>
+  </si>
+  <si>
+    <t>channel2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="238"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
@@ -110,9 +102,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,82 +438,133 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
         <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -533,136 +575,4 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83EB10EC-058D-1F49-A38A-7B2D1238154F}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
-        <v>12217</v>
-      </c>
-      <c r="C2" s="1">
-        <v>12273</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>62907</v>
-      </c>
-      <c r="C3" s="1">
-        <v>62941</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
-        <v>88247</v>
-      </c>
-      <c r="C4" s="1">
-        <v>88270</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1">
-        <v>113590</v>
-      </c>
-      <c r="C5" s="1">
-        <v>114437</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1">
-        <v>138917</v>
-      </c>
-      <c r="C6" s="1">
-        <v>138951</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1">
-        <v>71931</v>
-      </c>
-      <c r="C7" s="1">
-        <v>72083</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1">
-        <v>97251</v>
-      </c>
-      <c r="C8" s="1">
-        <v>97395</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1">
-        <v>147914</v>
-      </c>
-      <c r="C9" s="1">
-        <v>148024</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1">
-        <v>198568</v>
-      </c>
-      <c r="C10" s="1">
-        <v>198752</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1">
-        <v>261330</v>
-      </c>
-      <c r="C11" s="1">
-        <v>261461</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>